--- a/src/web技术.xlsx
+++ b/src/web技术.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23840"/>
+    <workbookView windowWidth="32460" windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
   <si>
     <t>前端开发语言</t>
   </si>
@@ -89,6 +89,9 @@
     <t>嵌入式</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>iOS</t>
   </si>
   <si>
@@ -99,13 +102,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="30"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
       <t>✅</t>
     </r>
     <r>
@@ -122,6 +118,20 @@
     <r>
       <rPr>
         <b/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="STHeiti Light"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（electron）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="20"/>
         <color theme="1"/>
         <rFont val="STHeiti Light"/>
@@ -183,7 +193,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +211,13 @@
     <font>
       <b/>
       <sz val="30"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
       <color theme="1"/>
       <name val="宋体-简"/>
       <charset val="134"/>
@@ -357,6 +374,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="STHeiti Light"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -591,6 +614,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -610,6 +646,73 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -635,7 +738,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -644,11 +747,28 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -657,9 +777,33 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -674,6 +818,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -687,127 +853,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -821,73 +866,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -896,6 +874,51 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1033,137 +1056,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1218,58 +1241,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1277,6 +1303,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1556,13 +1585,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1813,14 +1835,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:M36"/>
+  <dimension ref="A2:Q36"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="3" max="3" width="28.0769230769231" customWidth="1"/>
     <col min="4" max="4" width="21.3846153846154" customWidth="1"/>
     <col min="5" max="5" width="25.1923076923077" customWidth="1"/>
     <col min="6" max="6" width="18.4230769230769" customWidth="1"/>
-    <col min="7" max="7" width="24.8076923076923" customWidth="1"/>
+    <col min="7" max="7" width="25.7980769230769" customWidth="1"/>
     <col min="8" max="8" width="21.6153846153846" customWidth="1"/>
     <col min="9" max="9" width="14.2596153846154" customWidth="1"/>
     <col min="10" max="10" width="22.1538461538462" customWidth="1"/>
@@ -2024,7 +2046,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:17">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2037,7 +2059,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:17">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2051,7 +2073,7 @@
       <c r="K18" s="1"/>
     </row>
     <row r="19" ht="17.55"/>
-    <row r="20" ht="40.75" spans="3:13">
+    <row r="20" ht="40.75" spans="1:17">
       <c r="C20" s="3" t="s">
         <v>0</v>
       </c>
@@ -2064,311 +2086,320 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="29"/>
-    </row>
-    <row r="21" ht="40" spans="3:13">
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="16" t="s">
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" ht="40" spans="1:17">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19" t="s">
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="19" t="s">
+      <c r="I21" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M21" s="30" t="s">
+      <c r="M21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" ht="40" spans="3:13">
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="10" t="s">
+    <row r="22" ht="40" spans="1:17">
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10" t="s">
+      <c r="I22" s="15"/>
+      <c r="J22" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="31"/>
-    </row>
-    <row r="23" ht="40" spans="3:13">
-      <c r="C23" s="9" t="s">
+      <c r="L22" s="15"/>
+      <c r="M22" s="16"/>
+    </row>
+    <row r="23" ht="40" spans="1:17">
+      <c r="C23" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="20" t="s">
+      <c r="F23" s="19"/>
+      <c r="G23" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="21"/>
-      <c r="M23" s="32" t="s">
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" ht="40" spans="3:13">
-      <c r="C24" s="11"/>
-      <c r="D24" s="10" t="s">
+      <c r="L23" s="19"/>
+      <c r="M23" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="40" spans="1:17">
+      <c r="C24" s="22"/>
+      <c r="D24" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="33"/>
-    </row>
-    <row r="25" ht="40" spans="3:13">
-      <c r="C25" s="11"/>
-      <c r="D25" s="10" t="s">
+      <c r="E24" s="23"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="25"/>
+    </row>
+    <row r="25" ht="40" spans="1:17">
+      <c r="C25" s="22"/>
+      <c r="D25" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="33"/>
-    </row>
-    <row r="26" ht="40" spans="3:13">
-      <c r="C26" s="11"/>
-      <c r="D26" s="10" t="s">
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="25"/>
+    </row>
+    <row r="26" ht="40" spans="1:17">
+      <c r="C26" s="22"/>
+      <c r="D26" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="33"/>
-    </row>
-    <row r="27" ht="40" spans="3:13">
-      <c r="C27" s="12"/>
-      <c r="D27" s="10" t="s">
+      <c r="E26" s="23"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="25"/>
+    </row>
+    <row r="27" ht="40" spans="1:17">
+      <c r="C27" s="26"/>
+      <c r="D27" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="34"/>
-    </row>
-    <row r="28" ht="40" spans="3:13">
-      <c r="C28" s="9" t="s">
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="29"/>
+      <c r="Q27" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="10" t="s">
+    </row>
+    <row r="28" ht="40" spans="1:17">
+      <c r="C28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="20" t="s">
+      <c r="F28" s="19"/>
+      <c r="G28" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L28" s="20" t="s">
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="M28" s="35"/>
-    </row>
-    <row r="29" ht="40" spans="3:13">
-      <c r="C29" s="11"/>
-      <c r="D29" s="10" t="s">
+      <c r="L28" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M28" s="30"/>
+    </row>
+    <row r="29" ht="40" spans="1:17">
+      <c r="C29" s="22"/>
+      <c r="D29" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="36"/>
-    </row>
-    <row r="30" ht="40" spans="3:13">
-      <c r="C30" s="12"/>
-      <c r="D30" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="37"/>
-    </row>
-    <row r="31" ht="72" spans="3:13">
-      <c r="C31" s="13" t="s">
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="31"/>
+    </row>
+    <row r="30" ht="40" spans="1:17">
+      <c r="C30" s="26"/>
+      <c r="D30" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="26" t="s">
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="32"/>
+    </row>
+    <row r="31" ht="72" spans="1:17">
+      <c r="C31" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="27" t="s">
+      <c r="D31" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="27" t="s">
+      <c r="I31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="27" t="s">
+      <c r="J31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="K31" s="27" t="s">
+      <c r="K31" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="31"/>
-    </row>
-    <row r="32" ht="40" spans="3:13">
-      <c r="C32" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="20" t="s">
+      <c r="L31" s="15"/>
+      <c r="M31" s="16"/>
+    </row>
+    <row r="32" ht="40" spans="1:17">
+      <c r="C32" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="20" t="s">
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L32" s="21"/>
-      <c r="M32" s="35"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="30"/>
     </row>
     <row r="33" ht="40" spans="3:13">
-      <c r="C33" s="11"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="22"/>
+      <c r="D33" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="36"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="31"/>
     </row>
     <row r="34" ht="40" spans="3:13">
-      <c r="C34" s="11"/>
-      <c r="D34" s="10" t="s">
+      <c r="C34" s="22"/>
+      <c r="D34" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="36"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="31"/>
     </row>
     <row r="35" ht="40" spans="3:13">
-      <c r="C35" s="12"/>
-      <c r="D35" s="10" t="s">
+      <c r="C35" s="26"/>
+      <c r="D35" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="37"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="32"/>
     </row>
     <row r="36" ht="72.75" spans="3:13">
-      <c r="C36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="28" t="s">
+      <c r="C36" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="38"/>
+      <c r="D36" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="37">
